--- a/data/trans_camb/P16A01-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P16A01-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 5,02</t>
+          <t>-0,71; 4,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 1,95</t>
+          <t>-3,35; 2,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 2,54</t>
+          <t>-3,41; 2,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,06; 3,9</t>
+          <t>0,07; 3,93</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 3,61</t>
+          <t>-0,92; 3,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,34</t>
+          <t>0,4; 4,25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,71</t>
+          <t>0,32; 3,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 2,0</t>
+          <t>-1,47; 2,06</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 2,62</t>
+          <t>-0,54; 2,72</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 61,58</t>
+          <t>-7,74; 60,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-34,6; 25,6</t>
+          <t>-31,83; 26,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-31,99; 33,43</t>
+          <t>-33,48; 29,62</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 79,79</t>
+          <t>0,76; 81,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-11,55; 72,06</t>
+          <t>-14,36; 71,34</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,58; 87,77</t>
+          <t>4,83; 85,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,1; 55,37</t>
+          <t>3,76; 55,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-16,98; 30,25</t>
+          <t>-18,37; 30,57</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-10,22; 38,62</t>
+          <t>-7,0; 40,78</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 4,45</t>
+          <t>1,03; 4,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,63</t>
+          <t>0,09; 3,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 1,51</t>
+          <t>-2,21; 1,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,1; 4,74</t>
+          <t>1,04; 4,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,07; 4,65</t>
+          <t>1,03; 4,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 2,81</t>
+          <t>-1,42; 2,65</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,65; 4,12</t>
+          <t>1,51; 3,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,09; 3,58</t>
+          <t>1,23; 3,54</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 1,55</t>
+          <t>-1,28; 1,65</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,7; 90,69</t>
+          <t>14,61; 87,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,93; 73,35</t>
+          <t>0,77; 69,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-36,25; 29,16</t>
+          <t>-34,48; 30,34</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15,62; 91,17</t>
+          <t>15,41; 97,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,07; 89,95</t>
+          <t>14,34; 91,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-20,31; 54,78</t>
+          <t>-20,3; 50,34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,77; 78,41</t>
+          <t>23,74; 75,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16,39; 67,03</t>
+          <t>19,2; 67,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-19,53; 28,79</t>
+          <t>-19,52; 31,18</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 7,49</t>
+          <t>-0,26; 7,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 4,22</t>
+          <t>-2,52; 3,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 5,67</t>
+          <t>-1,0; 5,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 2,13</t>
+          <t>-5,34; 1,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 2,44</t>
+          <t>-4,44; 2,6</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 0,8</t>
+          <t>-5,31; 0,94</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 3,92</t>
+          <t>-1,62; 3,78</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 2,44</t>
+          <t>-2,61; 2,13</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 2,65</t>
+          <t>-2,15; 2,39</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 152,5</t>
+          <t>-8,1; 143,88</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-29,36; 90,13</t>
+          <t>-31,94; 75,83</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-14,16; 112,13</t>
+          <t>-13,71; 109,24</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-46,83; 29,38</t>
+          <t>-47,48; 26,05</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-40,95; 35,49</t>
+          <t>-40,26; 34,28</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-45,71; 12,16</t>
+          <t>-45,55; 13,38</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-18,44; 60,4</t>
+          <t>-18,38; 55,59</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-27,8; 37,02</t>
+          <t>-28,58; 30,57</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-23,83; 41,29</t>
+          <t>-24,37; 35,38</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,87</t>
+          <t>1,21; 3,85</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 2,13</t>
+          <t>-0,54; 2,19</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 1,11</t>
+          <t>-2,08; 1,07</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,65; 3,24</t>
+          <t>0,62; 3,13</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,47; 3,15</t>
+          <t>0,62; 3,28</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 2,02</t>
+          <t>-0,85; 2,01</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,31; 3,17</t>
+          <t>1,28; 3,1</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,26</t>
+          <t>0,53; 2,37</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 1,24</t>
+          <t>-0,92; 1,19</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>14,77; 59,11</t>
+          <t>16,59; 62,69</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 33,25</t>
+          <t>-7,13; 33,99</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-27,06; 16,34</t>
+          <t>-28,13; 16,14</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9,01; 55,87</t>
+          <t>8,75; 54,41</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,7; 54,15</t>
+          <t>8,57; 54,61</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-9,6; 34,21</t>
+          <t>-11,84; 33,63</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,36; 50,58</t>
+          <t>18,19; 49,85</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>5,62; 35,92</t>
+          <t>7,73; 39,11</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-12,1; 20,72</t>
+          <t>-13,12; 19,32</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A01-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P16A01-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-0,58</t>
+          <t>-1,19</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,21</t>
+          <t>2,29</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,97</t>
+          <t>0,77</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 4,76</t>
+          <t>-0,49; 4,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 2,05</t>
+          <t>-3,33; 1,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 2,29</t>
+          <t>-4,04; 1,65</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,07; 3,93</t>
+          <t>-0,12; 4,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 3,6</t>
+          <t>-0,79; 3,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,4; 4,25</t>
+          <t>0,39; 4,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,65</t>
+          <t>0,38; 3,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 2,06</t>
+          <t>-1,29; 1,97</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 2,72</t>
+          <t>-0,69; 2,38</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-6,31%</t>
+          <t>-12,97%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>10,51%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,74; 60,46</t>
+          <t>-4,43; 60,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-31,83; 26,51</t>
+          <t>-31,97; 24,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-33,48; 29,62</t>
+          <t>-39,49; 20,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,76; 81,43</t>
+          <t>-1,23; 80,85</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-14,36; 71,34</t>
+          <t>-11,9; 76,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,83; 85,78</t>
+          <t>6,16; 93,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,76; 55,47</t>
+          <t>5,18; 55,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-18,37; 30,57</t>
+          <t>-16,16; 29,94</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 40,78</t>
+          <t>-8,82; 36,19</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,11</t>
+          <t>0,87</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,78</t>
+          <t>1,63</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,33</t>
+          <t>1,25</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,03; 4,45</t>
+          <t>0,94; 4,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,09; 3,49</t>
+          <t>0,31; 3,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 1,57</t>
+          <t>-0,73; 2,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,04; 4,94</t>
+          <t>1,06; 4,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,03; 4,63</t>
+          <t>0,91; 4,55</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 2,65</t>
+          <t>0,09; 3,3</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,51; 3,99</t>
+          <t>1,52; 4,04</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,23; 3,54</t>
+          <t>1,07; 3,58</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 1,65</t>
+          <t>-0,01; 2,36</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-1,98%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>21,25%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,61; 87,93</t>
+          <t>14,93; 91,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,77; 69,73</t>
+          <t>4,44; 72,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-34,48; 30,34</t>
+          <t>-11,98; 53,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15,41; 97,63</t>
+          <t>15,3; 91,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,34; 91,67</t>
+          <t>12,75; 86,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-20,3; 50,34</t>
+          <t>0,59; 65,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,74; 75,82</t>
+          <t>23,74; 76,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>19,2; 67,6</t>
+          <t>16,86; 69,77</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-19,52; 31,18</t>
+          <t>-0,17; 45,77</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,25</t>
+          <t>2,1</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-2,16</t>
+          <t>-1,99</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,16</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 7,59</t>
+          <t>-0,1; 7,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 3,74</t>
+          <t>-2,19; 4,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 5,6</t>
+          <t>-1,09; 5,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 1,88</t>
+          <t>-5,8; 1,8</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 2,6</t>
+          <t>-4,62; 2,6</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 0,94</t>
+          <t>-5,72; 0,95</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 3,78</t>
+          <t>-1,49; 3,74</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 2,13</t>
+          <t>-2,44; 2,37</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 2,39</t>
+          <t>-2,18; 2,27</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-23,07%</t>
+          <t>-21,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-8,1; 143,88</t>
+          <t>-4,16; 149,95</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-31,94; 75,83</t>
+          <t>-27,8; 85,3</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-13,71; 109,24</t>
+          <t>-14,09; 101,96</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-47,48; 26,05</t>
+          <t>-50,3; 26,66</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-40,26; 34,28</t>
+          <t>-40,74; 36,24</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-45,55; 13,38</t>
+          <t>-46,34; 14,97</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-18,38; 55,59</t>
+          <t>-16,81; 57,2</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-28,58; 30,57</t>
+          <t>-27,11; 35,11</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-24,37; 35,38</t>
+          <t>-23,22; 35,09</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-0,3</t>
+          <t>0,29</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,71</t>
+          <t>1,28</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,22</t>
+          <t>0,8</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,21; 3,85</t>
+          <t>1,17; 4,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 2,19</t>
+          <t>-0,39; 2,19</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 1,07</t>
+          <t>-1,09; 1,66</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,62; 3,13</t>
+          <t>0,6; 3,21</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,62; 3,28</t>
+          <t>0,59; 3,25</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 2,01</t>
+          <t>0,25; 2,55</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,28; 3,1</t>
+          <t>1,3; 3,13</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,37</t>
+          <t>0,28; 2,14</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 1,19</t>
+          <t>-0,07; 1,65</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-4,28%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>11,92%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>16,59; 62,69</t>
+          <t>15,7; 63,42</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-7,13; 33,99</t>
+          <t>-5,37; 35,82</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-28,13; 16,14</t>
+          <t>-13,98; 25,76</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8,75; 54,41</t>
+          <t>8,67; 55,7</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,57; 54,61</t>
+          <t>8,02; 56,92</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-11,84; 33,63</t>
+          <t>3,4; 43,94</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,19; 49,85</t>
+          <t>18,14; 49,64</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>7,73; 39,11</t>
+          <t>3,48; 33,54</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-13,12; 19,32</t>
+          <t>-0,98; 25,79</t>
         </is>
       </c>
     </row>
